--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Real Madrid.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Real Madrid.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,212 +417,212 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>POSSind</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>POSSest</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OER</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>DER</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eFG%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>TOV%</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ORB%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>TOpts</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2CPts</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FastBPts</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TOunf</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rim FGM</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Rim FGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Rim_vol</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Paint FGM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Paint FGA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Paint_vol</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>MR FGM</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MR FGA</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>MR_vol</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Cor3 FGM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Cor3 FGA</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Cor3_vol</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ATB3 FGM</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ATB3 FGA</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ATB3_vol</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Rim %</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Paint %</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>MR %</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Cor3 %</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ATB3 %</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Rim PPS</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>MR PPS</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>3P PPS</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>TOptsPPO</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>2CPtsPPO</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>FastBPtsPPO</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Ass/TO</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Sh/TO</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Gen/TO</t>
         </is>
@@ -1161,259 +1149,259 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>2PM</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2PA</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>3PM</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>3PA</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>FTM</t>
         </is>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>FTA</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>DRB</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>ORB</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>BLK</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>BLK A.</t>
         </is>
       </c>
-      <c r="P7" s="1" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="Q7" s="1" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>TOunf</t>
         </is>
       </c>
-      <c r="R7" s="1" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="S7" s="1" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>F+</t>
         </is>
       </c>
-      <c r="T7" s="1" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>EFI</t>
         </is>
       </c>
-      <c r="U7" s="1" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>TOpts</t>
         </is>
       </c>
-      <c r="V7" s="1" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2CPts</t>
         </is>
       </c>
-      <c r="W7" s="1" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>FastBPts</t>
         </is>
       </c>
-      <c r="X7" s="1" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>FastB Opp</t>
         </is>
       </c>
-      <c r="Y7" s="1" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Rim FGM</t>
         </is>
       </c>
-      <c r="Z7" s="1" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Rim FGA</t>
         </is>
       </c>
-      <c r="AA7" s="1" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Rim %</t>
         </is>
       </c>
-      <c r="AB7" s="1" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Paint FGM</t>
         </is>
       </c>
-      <c r="AC7" s="1" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Paint FGA</t>
         </is>
       </c>
-      <c r="AD7" s="1" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Paint %</t>
         </is>
       </c>
-      <c r="AE7" s="1" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>MR FGM</t>
         </is>
       </c>
-      <c r="AF7" s="1" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>MR FGA</t>
         </is>
       </c>
-      <c r="AG7" s="1" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>MR %</t>
         </is>
       </c>
-      <c r="AH7" s="1" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>Cor3 FGM</t>
         </is>
       </c>
-      <c r="AI7" s="1" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>Cor3 FGA</t>
         </is>
       </c>
-      <c r="AJ7" s="1" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Cor3 %</t>
         </is>
       </c>
-      <c r="AK7" s="1" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>ATB3 FGM</t>
         </is>
       </c>
-      <c r="AL7" s="1" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>ATB3 FGA</t>
         </is>
       </c>
-      <c r="AM7" s="1" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>ATB3 %</t>
         </is>
       </c>
-      <c r="AN7" s="1" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="AO7" s="1" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>PLAYS</t>
         </is>
       </c>
-      <c r="AP7" s="1" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>eFG%</t>
         </is>
       </c>
-      <c r="AQ7" s="1" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>TS%</t>
         </is>
       </c>
-      <c r="AR7" s="1" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>PTS/PLAY</t>
         </is>
       </c>
-      <c r="AS7" s="1" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>TO%</t>
         </is>
       </c>
-      <c r="AT7" s="1" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="AU7" s="1" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>Ass/TO</t>
         </is>
       </c>
-      <c r="AV7" s="1" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>USG%</t>
         </is>
       </c>
-      <c r="AW7" s="1" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>OR%</t>
         </is>
       </c>
-      <c r="AX7" s="1" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>DR%</t>
         </is>
       </c>
-      <c r="AY7" s="1" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>pAST%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>#0 T. LYLES</t>
         </is>
@@ -1572,7 +1560,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>#1 D. KRAMER</t>
         </is>
@@ -1731,7 +1719,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>#5 M. SISSOKO</t>
         </is>
@@ -1890,7 +1878,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>#6 A. ABALDE</t>
         </is>
@@ -2049,7 +2037,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>#7 F. CAMPAZZO</t>
         </is>
@@ -2208,7 +2196,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>#11 M. HEZONJA</t>
         </is>
@@ -2367,7 +2355,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>#12 T. MALEDON</t>
         </is>
@@ -2526,7 +2514,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>#13 I. ALMANSA</t>
         </is>
@@ -2685,7 +2673,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>#14 G. DECK</t>
         </is>
@@ -2844,7 +2832,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>#23 S. LLULL</t>
         </is>
@@ -3003,7 +2991,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>#24 A. FELIZ</t>
         </is>
@@ -3162,7 +3150,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>#77 Ö. YURTSEVEN</t>
         </is>
@@ -3321,7 +3309,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Equip</t>
         </is>
@@ -3480,7 +3468,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -3639,7 +3627,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Rival</t>
         </is>
@@ -3798,7 +3786,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>--- PER GAME STATS ---</t>
         </is>
@@ -3855,7 +3843,7 @@
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>#0 T. LYLES (Per Game)</t>
         </is>
@@ -4014,7 +4002,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>#1 D. KRAMER (Per Game)</t>
         </is>
@@ -4173,7 +4161,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>#5 M. SISSOKO (Per Game)</t>
         </is>
@@ -4332,7 +4320,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>#6 A. ABALDE (Per Game)</t>
         </is>
@@ -4491,7 +4479,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>#7 F. CAMPAZZO (Per Game)</t>
         </is>
@@ -4650,7 +4638,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>#11 M. HEZONJA (Per Game)</t>
         </is>
@@ -4809,7 +4797,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>#12 T. MALEDON (Per Game)</t>
         </is>
@@ -4968,7 +4956,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>#13 I. ALMANSA (Per Game)</t>
         </is>
@@ -5127,7 +5115,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>#14 G. DECK (Per Game)</t>
         </is>
@@ -5286,7 +5274,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>#23 S. LLULL (Per Game)</t>
         </is>
@@ -5445,7 +5433,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>#24 A. FELIZ (Per Game)</t>
         </is>
@@ -5604,7 +5592,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>#77 Ö. YURTSEVEN (Per Game)</t>
         </is>
@@ -5763,7 +5751,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Equip (Per Game)</t>
         </is>
@@ -5922,7 +5910,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>TOTAL (Per Game)</t>
         </is>
@@ -6081,7 +6069,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Rival (Per Game)</t>
         </is>
